--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00717-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00717-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EC10F81-6D72-4673-AD38-DBB5CBA171BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1F4A2DA-55E1-4D21-B776-1FDA3EE3C3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{45F91C22-1EBC-476B-BBA5-1B3C6B3B184A}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{E28228C2-7F9D-4F31-9860-638E3265F8AC}"/>
   </bookViews>
   <sheets>
     <sheet name="00717-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1639,25 +1639,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27B8BE01-B599-487C-9688-99CC781650EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4FE619-5E04-4180-BBD4-D0135D65622F}">
   <dimension ref="A1:R46"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1685,7 +1685,7 @@
       <c r="Q1" s="34"/>
       <c r="R1" s="26"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1715,7 +1715,7 @@
       <c r="Q2" s="36"/>
       <c r="R2" s="37"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1811,7 +1811,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>2026</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="44"/>
       <c r="C6" s="46"/>
@@ -1891,7 +1891,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="51">
         <v>2025</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="53">
         <v>2024</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="51">
         <v>2023</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="53">
         <v>2022</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="51">
         <v>2021</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>27</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>27</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>27</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="53">
         <v>2020</v>
       </c>
@@ -3391,7 +3391,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>27</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>27</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>27</v>
       </c>
@@ -3559,7 +3559,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>27</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="51">
         <v>2019</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>4.54</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>27</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>27</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>27</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>27</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="53">
         <v>2018</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>27</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>27</v>
       </c>
@@ -4059,7 +4059,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="51" t="s">
         <v>82</v>
       </c>
